--- a/tests/testdata/office/Excel/セル内容.xlsx
+++ b/tests/testdata/office/Excel/セル内容.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\tebunko_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{383E9E34-A6EF-4368-B36F-C9167B5AAF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56B5FE6B-AE02-425A-AE4E-185AD5A2B479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{B5C7F786-6C59-4DF6-8080-97E78632DF74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14685" xr2:uid="{60CA3CDA-059D-4C5C-AAFA-04198A6E10DC}"/>
   </bookViews>
   <sheets>
     <sheet name="文字列" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <author>test</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{29A023E2-D41B-4238-BFED-4F30552AA9A5}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{02EDB30E-B5A1-40E4-A74F-00C359BC3DBF}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="539">
   <si>
     <t>ID</t>
   </si>
@@ -1682,6 +1682,12 @@
   </si>
   <si>
     <t>選択肢A</t>
+  </si>
+  <si>
+    <t>TC10-O05</t>
+  </si>
+  <si>
+    <t>ヘッダー・フッター</t>
   </si>
   <si>
     <t>リンクの表示文字列</t>
@@ -1870,7 +1876,7 @@
         <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45A5D5A7-FD54-32CF-75F2-6A1FEE50A591}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD8616C-1CF5-47E3-B529-603C5EDA8F61}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2245,7 +2251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6F58BD-D368-47B8-AA13-EFB87B9DAB95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8393B3-2AD5-4145-A6DE-51CAC97849CA}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -2614,7 +2620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8780B09E-9DFF-4BBB-B552-85B3F5F8E309}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8176C640-F049-41C9-A088-A99A7C10BC88}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
@@ -2943,7 +2949,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C900163-5EF0-4113-ACAF-039E91557202}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56DD7DD4-5A14-4754-9D55-136CF4A151AA}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -3164,7 +3170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2704FBFB-1D93-48DF-8A65-60B43D5A9558}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FD6BF23-349C-4665-B087-5170F988A678}">
   <sheetPr filterMode="1"/>
   <dimension ref="A2:KN300"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -4165,7 +4171,7 @@
       <c r="AZ300" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A11:C15" xr:uid="{2704FBFB-1D93-48DF-8A65-60B43D5A9558}">
+  <autoFilter ref="A11:C15" xr:uid="{6FD6BF23-349C-4665-B087-5170F988A678}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val="絞込"/>
@@ -4181,8 +4187,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5998EB62-9C9B-4580-ADE3-6FD3B552D71B}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CC71B6-6FD8-48F9-AF82-35417E7844F0}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4226,7 +4232,7 @@
         <v>532</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4240,20 +4246,29 @@
         <v>535</v>
       </c>
     </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{557F3955-79D0-47B7-8CB3-B0F08EF1FD6B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{96EF63F4-43EF-4A16-B530-6741EC8C228D}">
       <formula1>"選択肢A,選択肢B"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{51997399-1A61-41E0-B09F-3C3A474DEBDC}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{F08B0F76-C65A-4A01-A2AD-8DEE827B6339}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <headerFooter>
-    <oddHeader>&amp;CTC10 ヘッダーのテキスト</oddHeader>
+    <oddHeader>&amp;CTC10 ヘッダーのテキスト&amp;LTC10-O05 左ヘッダー&amp;RTC10-O05 右ヘッダー</oddHeader>
+    <oddFooter>&amp;CTC10-O05 通常フッター&amp;LTC10-O05 左フッター&amp;R&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>
